--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Coviran Granada.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Coviran Granada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>67.994</v>
+        <v>99.60169999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>71.4842</v>
+        <v>103.5819</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.490400000000001</v>
+        <v>-3.9807</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.0951</v>
+        <v>-6.738700000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-11.6038</v>
+        <v>-5.544100000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4909999999999996</v>
+        <v>-1.1945</v>
       </c>
       <c r="J2" t="n">
-        <v>33.0639</v>
+        <v>52.4736</v>
       </c>
       <c r="K2" t="n">
-        <v>16.3865</v>
+        <v>32.0615</v>
       </c>
       <c r="L2" t="n">
-        <v>16.6769</v>
+        <v>20.4125</v>
       </c>
       <c r="M2" t="n">
-        <v>-45.1587</v>
+        <v>-59.2126</v>
       </c>
       <c r="N2" t="n">
-        <v>-27.991</v>
+        <v>-37.6054</v>
       </c>
       <c r="O2" t="n">
-        <v>-17.1678</v>
+        <v>-21.6071</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.856100000000001</v>
+        <v>-10.0156</v>
       </c>
       <c r="Q2" t="n">
-        <v>-58.7499</v>
+        <v>-76.2568</v>
       </c>
       <c r="R2" t="n">
-        <v>54.8938</v>
+        <v>66.2407</v>
       </c>
       <c r="S2" t="n">
-        <v>15.8125</v>
+        <v>24.9258</v>
       </c>
       <c r="T2" t="n">
-        <v>12.2618</v>
+        <v>18.7715</v>
       </c>
       <c r="U2" t="n">
-        <v>3.550799999999999</v>
+        <v>6.1546</v>
       </c>
       <c r="V2" t="n">
-        <v>68.13209999999999</v>
+        <v>91.4301</v>
       </c>
       <c r="W2" t="n">
-        <v>84.9084</v>
+        <v>108.5934</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.7761</v>
+        <v>-17.1629</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>5.026800000000001</v>
+        <v>5.1186</v>
       </c>
       <c r="E3" t="n">
-        <v>1.486599999999999</v>
+        <v>1.2962</v>
       </c>
       <c r="F3" t="n">
-        <v>3.540299999999999</v>
+        <v>3.823</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.8649</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0983</v>
+        <v>4.0739</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2783</v>
+        <v>-2.2091</v>
       </c>
       <c r="J3" t="n">
-        <v>9.543199999999999</v>
+        <v>9.387700000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>7.1177</v>
+        <v>6.9674</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4257</v>
+        <v>2.4202</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.7234</v>
+        <v>-7.522700000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.0191</v>
+        <v>-2.8933</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.7042</v>
+        <v>-4.6294</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13.1563</v>
+        <v>-13.2027</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1147</v>
+        <v>11.1539</v>
       </c>
       <c r="S3" t="n">
-        <v>11.1811</v>
+        <v>11.2173</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5853</v>
+        <v>4.6229</v>
       </c>
       <c r="U3" t="n">
-        <v>6.5958</v>
+        <v>6.594399999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.9326</v>
+        <v>-5.9147</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5144000000000001</v>
+        <v>0.4882</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.4472</v>
+        <v>-6.403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>A. FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06689999999999929</v>
+        <v>1.98</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7959</v>
+        <v>2.8289</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.7286</v>
+        <v>-0.8488999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1837</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.0009</v>
+        <v>1.379</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.817399999999999</v>
+        <v>-0.8460999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>16.8173</v>
+        <v>1.1064</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0856</v>
+        <v>1.8961</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7316</v>
+        <v>-0.7896</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.6338</v>
+        <v>-0.5735999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.0848</v>
+        <v>-0.5171</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.5491</v>
+        <v>-0.05649999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-9.3001</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.9519</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>15.6516</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>5.4003</v>
+        <v>0.13</v>
       </c>
       <c r="T4" t="n">
-        <v>9.046299999999999</v>
+        <v>0.0882</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6458</v>
+        <v>0.0418</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7829</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8837</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.1007</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>I. AURRECOECHEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8113000000000001</v>
+        <v>-1.5242</v>
       </c>
       <c r="E5" t="n">
-        <v>7.619599999999999</v>
+        <v>-0.8348</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.4312</v>
+        <v>-0.6894</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3081</v>
+        <v>-0.7548000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1911000000000003</v>
+        <v>-1.488</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1171</v>
+        <v>0.7331</v>
       </c>
       <c r="J5" t="n">
-        <v>27.6387</v>
+        <v>-0.7552</v>
       </c>
       <c r="K5" t="n">
-        <v>20.0261</v>
+        <v>-0.7552</v>
       </c>
       <c r="L5" t="n">
-        <v>7.6126</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-22.3304</v>
+        <v>0.0002999999999999947</v>
       </c>
       <c r="N5" t="n">
-        <v>-19.8353</v>
+        <v>-0.7328</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4955</v>
+        <v>0.7331</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.361</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-37.8813</v>
+        <v>-2.504</v>
       </c>
       <c r="R5" t="n">
-        <v>36.5202</v>
+        <v>0.4552</v>
       </c>
       <c r="S5" t="n">
-        <v>5.9619</v>
+        <v>2.211</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5886</v>
+        <v>2.2666</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3737</v>
+        <v>-0.0556</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.7208</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>13.2734</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-23.994</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.536</v>
+        <v>-2.6772</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8300000000000001</v>
+        <v>19.2926</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7060000000000001</v>
+        <v>-21.9698</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7643</v>
+        <v>1.7515</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4921</v>
+        <v>11.3568</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7277</v>
+        <v>-9.605499999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7517</v>
+        <v>22.4505</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7517</v>
+        <v>17.572</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.8779</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01260000000000006</v>
+        <v>-20.6988</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7404000000000001</v>
+        <v>-6.2153</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7277</v>
+        <v>-14.4837</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0415</v>
+        <v>-10.2434</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-29.5926</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4536</v>
+        <v>19.349</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2018</v>
+        <v>5.8523</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2562</v>
+        <v>10.8365</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.05439999999999999</v>
+        <v>-4.9844</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9319999999999999</v>
+        <v>-0.03760000000000002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>15.5979</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-15.6352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.5852</v>
+        <v>-5.887000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7110000000000003</v>
+        <v>7.6061</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.2964</v>
+        <v>-13.4928</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.4774</v>
+        <v>7.847200000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.2897</v>
+        <v>1.7103</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8124</v>
+        <v>6.1367</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5693</v>
+        <v>33.4943</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.053</v>
+        <v>24.6687</v>
       </c>
       <c r="L7" t="n">
-        <v>7.622400000000001</v>
+        <v>8.8248</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.0468</v>
+        <v>-25.6473</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.2366</v>
+        <v>-22.9585</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.81</v>
+        <v>-2.6883</v>
       </c>
       <c r="P7" t="n">
-        <v>6.1246</v>
+        <v>0.2276000000000005</v>
       </c>
       <c r="Q7" t="n">
-        <v>-13.8367</v>
+        <v>-43.0224</v>
       </c>
       <c r="R7" t="n">
-        <v>19.9613</v>
+        <v>43.25</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7061</v>
+        <v>3.741400000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1123</v>
+        <v>5.1772</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.8182</v>
+        <v>-1.4351</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5262</v>
+        <v>-17.703</v>
       </c>
       <c r="W7" t="n">
-        <v>9.866299999999999</v>
+        <v>11.9576</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.3925</v>
+        <v>-29.6605</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.9355</v>
+        <v>-7.5313</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.7201</v>
+        <v>-3.4439</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2154999999999998</v>
+        <v>-4.0872</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.5886</v>
+        <v>-7.3171</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8547</v>
+        <v>-0.3845999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.734</v>
+        <v>-6.9323</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1101</v>
+        <v>-0.5920999999999998</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3289</v>
+        <v>1.2271</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.439</v>
+        <v>-1.8192</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.4786</v>
+        <v>-6.725000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1838</v>
+        <v>-1.6118</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2947</v>
+        <v>-5.113300000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7219</v>
+        <v>6.1459</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5879</v>
+        <v>-1.5935</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3097</v>
+        <v>7.7393</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.137</v>
+        <v>-3.2494</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.251</v>
+        <v>-0.4844</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8859</v>
+        <v>-2.7646</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9319</v>
+        <v>-3.1107</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-2.3368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.7707</v>
+        <v>-9.465800000000002</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.4296</v>
+        <v>-1.093800000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6589000000000003</v>
+        <v>-8.3718</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0976</v>
+        <v>-22.5377</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9604000000000001</v>
+        <v>-17.2383</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1371</v>
+        <v>-5.2995</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6535000000000001</v>
+        <v>1.724399999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4667</v>
+        <v>-4.0867</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1202</v>
+        <v>5.811300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4442</v>
+        <v>-24.2623</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4272</v>
+        <v>-13.1516</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0169</v>
+        <v>-11.1104</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>4.5526</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.073399999999999</v>
+        <v>-17.983</v>
       </c>
       <c r="R9" t="n">
-        <v>10.4343</v>
+        <v>22.5357</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.1893</v>
+        <v>10.0309</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.3419</v>
+        <v>3.868</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8475</v>
+        <v>6.162599999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8449</v>
+        <v>-1.5116</v>
       </c>
       <c r="W9" t="n">
-        <v>1.639</v>
+        <v>11.2967</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.4839</v>
+        <v>-12.8081</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.0789</v>
+        <v>-10.7141</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.158799999999999</v>
+        <v>-11.5707</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9199</v>
+        <v>0.8567000000000007</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.3978</v>
+        <v>-5.0428</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0957</v>
+        <v>-0.8967999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3022</v>
+        <v>-4.1461</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.4892</v>
+        <v>-0.7573000000000002</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4400000000000001</v>
+        <v>0.4299000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.0491</v>
+        <v>-1.1872</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9089</v>
+        <v>-4.2856</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6556</v>
+        <v>-1.3267</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2531</v>
+        <v>-2.9589</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.134</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-9.1053</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2684</v>
+        <v>10.4711</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.818</v>
+        <v>-5.2077</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2672</v>
+        <v>-3.3422</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5506</v>
+        <v>-1.8653</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7291</v>
+        <v>-1.8296</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7291</v>
+        <v>-3.4638</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.4645</v>
+        <v>-12.5165</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9388</v>
+        <v>-3.5571</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.525500000000001</v>
+        <v>-8.9596</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2027000000000001</v>
+        <v>-0.2262999999999995</v>
       </c>
       <c r="H11" t="n">
-        <v>-15.4696</v>
+        <v>-15.3874</v>
       </c>
       <c r="I11" t="n">
-        <v>15.2672</v>
+        <v>15.1611</v>
       </c>
       <c r="J11" t="n">
-        <v>16.5781</v>
+        <v>16.1051</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2167000000000002</v>
+        <v>0.02209999999999926</v>
       </c>
       <c r="L11" t="n">
-        <v>16.3613</v>
+        <v>16.0828</v>
       </c>
       <c r="M11" t="n">
-        <v>-16.7806</v>
+        <v>-16.3313</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.6865</v>
+        <v>-15.4096</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0942</v>
+        <v>-0.9219000000000002</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8148</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-27.9006</v>
+        <v>-27.9989</v>
       </c>
       <c r="R11" t="n">
-        <v>26.0858</v>
+        <v>26.1778</v>
       </c>
       <c r="S11" t="n">
-        <v>-11.7132</v>
+        <v>-11.7477</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.0103</v>
+        <v>-7.0024</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.7029</v>
+        <v>-4.745</v>
       </c>
       <c r="V11" t="n">
-        <v>1.266000000000001</v>
+        <v>1.2782</v>
       </c>
       <c r="W11" t="n">
-        <v>15.394</v>
+        <v>15.3389</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.128</v>
+        <v>-14.0607</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.3136</v>
+        <v>-13.3053</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.0942</v>
+        <v>-13.4253</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2193999999999998</v>
+        <v>0.1201000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.1084</v>
+        <v>-19.0556</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.0608</v>
+        <v>-6.0327</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.0476</v>
+        <v>-13.0226</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7101</v>
+        <v>-1.9382</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2574</v>
+        <v>1.127</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9675</v>
+        <v>-3.0656</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.3984</v>
+        <v>-17.1173</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.3184</v>
+        <v>-7.160200000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.0799</v>
+        <v>-9.956899999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.0126</v>
+        <v>-17.0726</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04849999999999977</v>
+        <v>0.04690000000000015</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9283999999999997</v>
+        <v>-0.91</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9768999999999999</v>
+        <v>0.9566000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>5.746599999999999</v>
+        <v>5.7033</v>
       </c>
       <c r="W12" t="n">
-        <v>6.556699999999999</v>
+        <v>6.495299999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8102</v>
+        <v>-0.7918999999999997</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.0222</v>
+        <v>-14.1761</v>
       </c>
       <c r="E13" t="n">
-        <v>2.796200000000001</v>
+        <v>-10.2508</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.8183</v>
+        <v>-3.9253</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.7133</v>
+        <v>-7.7455</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.3023</v>
+        <v>-1.7852</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.4107</v>
+        <v>-5.9602</v>
       </c>
       <c r="J13" t="n">
-        <v>16.0682</v>
+        <v>-4.1204</v>
       </c>
       <c r="K13" t="n">
-        <v>11.0348</v>
+        <v>0.7443000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5.033300000000001</v>
+        <v>-4.8648</v>
       </c>
       <c r="M13" t="n">
-        <v>-28.781</v>
+        <v>-3.6248</v>
       </c>
       <c r="N13" t="n">
-        <v>-17.337</v>
+        <v>-2.5297</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.4442</v>
+        <v>-1.0953</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.5273</v>
+        <v>-2.5038</v>
       </c>
       <c r="Q13" t="n">
-        <v>-37.6544</v>
+        <v>-5.6909</v>
       </c>
       <c r="R13" t="n">
-        <v>28.1274</v>
+        <v>3.187</v>
       </c>
       <c r="S13" t="n">
-        <v>3.390899999999999</v>
+        <v>-3.2985</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0429</v>
+        <v>-1.5291</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3482999999999998</v>
+        <v>-1.7694</v>
       </c>
       <c r="V13" t="n">
-        <v>4.827</v>
+        <v>-0.6281000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>21.3396</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.5126</v>
+        <v>-1.7176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.7898</v>
+        <v>-15.9295</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.378</v>
+        <v>-14.0493</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.411799999999999</v>
+        <v>-1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.1759</v>
+        <v>-9.2277</v>
       </c>
       <c r="H14" t="n">
-        <v>-11.4545</v>
+        <v>-6.516</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.721399999999999</v>
+        <v>-2.7118</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.5344</v>
+        <v>-5.7373</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.3041</v>
+        <v>-2.204</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7698</v>
+        <v>-3.5332</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.6417</v>
+        <v>-3.4905</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.150500000000001</v>
+        <v>-4.3119</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.4909</v>
+        <v>0.8214</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6709</v>
+        <v>-0.4552000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.1148</v>
+        <v>-5.007899999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>16.7858</v>
+        <v>4.5526</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2275</v>
+        <v>-4.345499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8102999999999999</v>
+        <v>-3.3043</v>
       </c>
       <c r="U14" t="n">
-        <v>4.038</v>
+        <v>-1.0412</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.5123</v>
+        <v>-1.9009</v>
       </c>
       <c r="W14" t="n">
-        <v>4.0816</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.5939</v>
+        <v>-1.9009</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.9432</v>
+        <v>-16.4759</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.9336</v>
+        <v>0.6258000000000008</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0095</v>
+        <v>-17.1018</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.2522</v>
+        <v>-9.215199999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.5546</v>
+        <v>-3.2292</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6975</v>
+        <v>-5.985800000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.6436</v>
+        <v>25.274</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.1727</v>
+        <v>17.3251</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.4711</v>
+        <v>7.948899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6085</v>
+        <v>-34.4891</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.3818</v>
+        <v>-20.5544</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7734000000000001</v>
+        <v>-13.9346</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4536000000000001</v>
+        <v>-19.8043</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.9904</v>
+        <v>-56.2251</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5366</v>
+        <v>36.4213</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.3283</v>
+        <v>4.518400000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.2996</v>
+        <v>3.6944</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0287</v>
+        <v>0.8242999999999998</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.909</v>
+        <v>8.0245</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>27.883</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.909</v>
+        <v>-19.8582</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-18.4226</v>
+        <v>-18.4342</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.6148</v>
+        <v>-12.7033</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.807799999999999</v>
+        <v>-5.7309</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.1049</v>
+        <v>-10.0952</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.933400000000001</v>
+        <v>-5.9337</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.1715</v>
+        <v>-4.1615</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.9347</v>
+        <v>-5.9968</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.1522</v>
+        <v>-2.1975</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.7825</v>
+        <v>-3.7992</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.1702</v>
+        <v>-4.0984</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.7812</v>
+        <v>-3.7362</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3889999999999999</v>
+        <v>-0.3623</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.6708</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.9153</v>
+        <v>-2.9246</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.102</v>
+        <v>-2.1052</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8134</v>
+        <v>-0.8194</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0926</v>
+        <v>-1.0894</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.5951</v>
+        <v>-24.4285</v>
       </c>
       <c r="E17" t="n">
-        <v>-24.6961</v>
+        <v>-6.441400000000002</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8988</v>
+        <v>-17.9874</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.7034</v>
+        <v>-18.3541</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.5566</v>
+        <v>-18.0974</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.1465</v>
+        <v>-0.2569000000000008</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.8009</v>
+        <v>3.0573</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2281</v>
+        <v>-4.537799999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.5728</v>
+        <v>7.595099999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.9025</v>
+        <v>-21.4116</v>
       </c>
       <c r="N17" t="n">
-        <v>-6.3287</v>
+        <v>-13.5597</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5738</v>
+        <v>-7.852</v>
       </c>
       <c r="P17" t="n">
-        <v>-9.3001</v>
+        <v>7.739599999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.4565</v>
+        <v>-19.8039</v>
       </c>
       <c r="R17" t="n">
-        <v>13.1565</v>
+        <v>27.5436</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.9983</v>
+        <v>-10.0688</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.0123</v>
+        <v>-4.345600000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9858000000000001</v>
+        <v>-5.7229</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4066</v>
+        <v>-3.744800000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>10.5735</v>
+        <v>14.6514</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.167</v>
+        <v>-18.3961</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.9145</v>
+        <v>-28.7011</v>
       </c>
       <c r="E18" t="n">
-        <v>-31.5451</v>
+        <v>-25.1621</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3693999999999998</v>
+        <v>-3.5392</v>
       </c>
       <c r="G18" t="n">
-        <v>-20.9994</v>
+        <v>-15.7332</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.718100000000001</v>
+        <v>-8.553100000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-15.2815</v>
+        <v>-7.1798</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.375</v>
+        <v>-7.134399999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3026999999999997</v>
+        <v>-2.3973</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.0723</v>
+        <v>-4.736799999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.6242</v>
+        <v>-8.598700000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-5.4152</v>
+        <v>-6.1556</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.2091</v>
+        <v>-2.4431</v>
       </c>
       <c r="P18" t="n">
-        <v>-10.6611</v>
+        <v>-9.332800000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-30.6224</v>
+        <v>-22.5356</v>
       </c>
       <c r="R18" t="n">
-        <v>19.9613</v>
+        <v>13.2029</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.9771</v>
+        <v>-7.0296</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.8924</v>
+        <v>-6.0148</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.0849</v>
+        <v>-1.0148</v>
       </c>
       <c r="V18" t="n">
-        <v>6.723100000000001</v>
+        <v>3.394699999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>11.3447</v>
+        <v>10.5226</v>
       </c>
       <c r="X18" t="n">
-        <v>-4.6214</v>
+        <v>-7.1279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-35.9458</v>
+        <v>-39.0301</v>
       </c>
       <c r="E19" t="n">
-        <v>-24.9649</v>
+        <v>-36.4637</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.9808</v>
+        <v>-2.5664</v>
       </c>
       <c r="G19" t="n">
-        <v>-25.3015</v>
+        <v>-27.3827</v>
       </c>
       <c r="H19" t="n">
-        <v>-13.2559</v>
+        <v>-6.240099999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-12.0455</v>
+        <v>-21.1424</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4099000000000004</v>
+        <v>-12.2123</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4990000000000006</v>
+        <v>-0.3848999999999997</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08920000000000017</v>
+        <v>-11.8271</v>
       </c>
       <c r="M19" t="n">
-        <v>-24.8916</v>
+        <v>-15.1706</v>
       </c>
       <c r="N19" t="n">
-        <v>-12.7568</v>
+        <v>-5.8553</v>
       </c>
       <c r="O19" t="n">
-        <v>-12.1345</v>
+        <v>-9.3154</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8146</v>
+        <v>-10.6987</v>
       </c>
       <c r="Q19" t="n">
-        <v>-27.9005</v>
+        <v>-33.0066</v>
       </c>
       <c r="R19" t="n">
-        <v>26.086</v>
+        <v>22.3079</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.4367</v>
+        <v>-6.723100000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3788</v>
+        <v>-2.6996</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.0579</v>
+        <v>-4.0239</v>
       </c>
       <c r="V19" t="n">
-        <v>-5.3928</v>
+        <v>5.774100000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7245</v>
+        <v>11.4543</v>
       </c>
       <c r="X19" t="n">
-        <v>-10.1173</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>-47.905</v>
+        <v>-48.9246</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.0628</v>
+        <v>-29.0718</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.8423</v>
+        <v>-19.8532</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.4623</v>
+        <v>-26.8912</v>
       </c>
       <c r="H20" t="n">
-        <v>-15.4426</v>
+        <v>-15.502</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01929999999999987</v>
+        <v>-11.3891</v>
       </c>
       <c r="J20" t="n">
-        <v>10.3204</v>
+        <v>10.1133</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06659999999999994</v>
+        <v>3.4154</v>
       </c>
       <c r="L20" t="n">
-        <v>10.2536</v>
+        <v>6.6982</v>
       </c>
       <c r="M20" t="n">
-        <v>-25.7826</v>
+        <v>-37.0044</v>
       </c>
       <c r="N20" t="n">
-        <v>-15.5094</v>
+        <v>-18.9176</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.2734</v>
+        <v>-18.0872</v>
       </c>
       <c r="P20" t="n">
-        <v>-26.9933</v>
+        <v>-7.5118</v>
       </c>
       <c r="Q20" t="n">
-        <v>-65.101</v>
+        <v>-43.0223</v>
       </c>
       <c r="R20" t="n">
-        <v>38.108</v>
+        <v>35.5105</v>
       </c>
       <c r="S20" t="n">
-        <v>-23.7552</v>
+        <v>-7.055299999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-17.7622</v>
+        <v>-4.2772</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.993</v>
+        <v>-2.778</v>
       </c>
       <c r="V20" t="n">
-        <v>18.3056</v>
+        <v>-7.4659</v>
       </c>
       <c r="W20" t="n">
-        <v>35.4801</v>
+        <v>8.1143</v>
       </c>
       <c r="X20" t="n">
-        <v>-17.1747</v>
+        <v>-15.5806</v>
       </c>
     </row>
     <row r="21">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
-        <v>-48.493</v>
+        <v>-59.4448</v>
       </c>
       <c r="E21" t="n">
-        <v>-13.2415</v>
+        <v>-17.2571</v>
       </c>
       <c r="F21" t="n">
-        <v>-35.2512</v>
+        <v>-42.1877</v>
       </c>
       <c r="G21" t="n">
-        <v>1.814</v>
+        <v>4.856700000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.3245</v>
+        <v>-14.225</v>
       </c>
       <c r="I21" t="n">
-        <v>13.1381</v>
+        <v>19.0816</v>
       </c>
       <c r="J21" t="n">
-        <v>29.5845</v>
+        <v>41.9074</v>
       </c>
       <c r="K21" t="n">
-        <v>3.933900000000001</v>
+        <v>6.3367</v>
       </c>
       <c r="L21" t="n">
-        <v>25.6507</v>
+        <v>35.5711</v>
       </c>
       <c r="M21" t="n">
-        <v>-27.7706</v>
+        <v>-37.0507</v>
       </c>
       <c r="N21" t="n">
-        <v>-15.2581</v>
+        <v>-20.5617</v>
       </c>
       <c r="O21" t="n">
-        <v>-12.5124</v>
+        <v>-16.4893</v>
       </c>
       <c r="P21" t="n">
-        <v>-8.3926</v>
+        <v>-14.3407</v>
       </c>
       <c r="Q21" t="n">
-        <v>-46.047</v>
+        <v>-61.0053</v>
       </c>
       <c r="R21" t="n">
-        <v>37.6544</v>
+        <v>46.6647</v>
       </c>
       <c r="S21" t="n">
-        <v>-24.7779</v>
+        <v>-30.3316</v>
       </c>
       <c r="T21" t="n">
-        <v>-13.2982</v>
+        <v>-15.3913</v>
       </c>
       <c r="U21" t="n">
-        <v>-11.4799</v>
+        <v>-14.9399</v>
       </c>
       <c r="V21" t="n">
-        <v>-17.1361</v>
+        <v>-19.6286</v>
       </c>
       <c r="W21" t="n">
-        <v>16.5192</v>
+        <v>17.2324</v>
       </c>
       <c r="X21" t="n">
-        <v>-33.6553</v>
+        <v>-36.8611</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,145 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-244.4392</v>
+        <v>-74.5311</v>
       </c>
       <c r="E22" t="n">
-        <v>-111.7148</v>
+        <v>-52.7534</v>
       </c>
       <c r="F22" t="n">
-        <v>-132.7236</v>
+        <v>-21.7779</v>
       </c>
       <c r="G22" t="n">
-        <v>-175.319</v>
+        <v>-21.2315</v>
       </c>
       <c r="H22" t="n">
-        <v>-120.079</v>
+        <v>-20.0831</v>
       </c>
       <c r="I22" t="n">
-        <v>-55.239</v>
+        <v>-1.1483</v>
       </c>
       <c r="J22" t="n">
-        <v>124.7705</v>
+        <v>16.2297</v>
       </c>
       <c r="K22" t="n">
-        <v>59.01739999999999</v>
+        <v>2.3898</v>
       </c>
       <c r="L22" t="n">
-        <v>65.7526</v>
+        <v>13.8399</v>
       </c>
       <c r="M22" t="n">
-        <v>-300.0893</v>
+        <v>-37.4613</v>
       </c>
       <c r="N22" t="n">
-        <v>-179.0974</v>
+        <v>-22.4728</v>
       </c>
       <c r="O22" t="n">
-        <v>-120.9916</v>
+        <v>-14.9879</v>
       </c>
       <c r="P22" t="n">
-        <v>-77.1229</v>
+        <v>-36.649</v>
       </c>
       <c r="Q22" t="n">
-        <v>-461.6061</v>
+        <v>-83.31319999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>384.4829</v>
+        <v>46.6648</v>
       </c>
       <c r="S22" t="n">
-        <v>-48.5279</v>
+        <v>-31.0811</v>
       </c>
       <c r="T22" t="n">
-        <v>-25.4612</v>
+        <v>-23.5153</v>
       </c>
       <c r="U22" t="n">
-        <v>-23.0654</v>
+        <v>-7.5655</v>
       </c>
       <c r="V22" t="n">
-        <v>56.52959999999999</v>
+        <v>14.4299</v>
       </c>
       <c r="W22" t="n">
-        <v>250.5813</v>
+        <v>37.8458</v>
       </c>
       <c r="X22" t="n">
-        <v>-194.0516</v>
+        <v>-23.4161</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Coviran Granada</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-296.997</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-102.847</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-194.1502</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-190.6962</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-128.6167</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-62.07899999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>194.0797</v>
+      </c>
+      <c r="K23" t="n">
+        <v>99.61970000000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>94.46000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-384.7763</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-228.2372</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-156.539</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-111.5396</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-573.6333999999999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>462.0938</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-60.3889</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-25.5961</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-34.7907</v>
+      </c>
+      <c r="V23" t="n">
+        <v>65.6277</v>
+      </c>
+      <c r="W23" t="n">
+        <v>302.3031</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-236.6745</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Coviran Granada.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Coviran Granada.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>99.60169999999999</v>
+        <v>81.0483</v>
       </c>
       <c r="E2" t="n">
-        <v>103.5819</v>
+        <v>90.19110000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9807</v>
+        <v>-9.1424</v>
       </c>
       <c r="G2" t="n">
         <v>-6.738700000000001</v>
@@ -610,13 +610,13 @@
         <v>66.2407</v>
       </c>
       <c r="S2" t="n">
-        <v>24.9258</v>
+        <v>6.372999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>18.7715</v>
+        <v>5.381</v>
       </c>
       <c r="U2" t="n">
-        <v>6.1546</v>
+        <v>0.9922999999999997</v>
       </c>
       <c r="V2" t="n">
         <v>91.4301</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>A. FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1186</v>
+        <v>2.2796</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2962</v>
+        <v>3.0657</v>
       </c>
       <c r="F3" t="n">
-        <v>3.823</v>
+        <v>-0.7861999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8649</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0739</v>
+        <v>1.379</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2091</v>
+        <v>-0.8460999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>9.387700000000001</v>
+        <v>1.1064</v>
       </c>
       <c r="K3" t="n">
-        <v>6.9674</v>
+        <v>1.8961</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4202</v>
+        <v>-0.7896</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.522700000000001</v>
+        <v>-0.5735999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.8933</v>
+        <v>-0.5171</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.6294</v>
+        <v>-0.05649999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0487</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13.2027</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1539</v>
+        <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>11.2173</v>
+        <v>0.4297</v>
       </c>
       <c r="T3" t="n">
-        <v>4.6229</v>
+        <v>0.3251</v>
       </c>
       <c r="U3" t="n">
-        <v>6.594399999999999</v>
+        <v>0.1046</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.9147</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4882</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.403</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.98</v>
+        <v>-2.0393</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8289</v>
+        <v>-2.759</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8488999999999999</v>
+        <v>0.7196999999999996</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5328000000000001</v>
+        <v>1.8649</v>
       </c>
       <c r="H4" t="n">
-        <v>1.379</v>
+        <v>4.0739</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8460999999999999</v>
+        <v>-2.2091</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1064</v>
+        <v>9.387700000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8961</v>
+        <v>6.9674</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7896</v>
+        <v>2.4202</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5735999999999999</v>
+        <v>-7.522700000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5171</v>
+        <v>-2.8933</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05649999999999999</v>
+        <v>-4.6294</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2276</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-13.2027</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2276</v>
+        <v>11.1539</v>
       </c>
       <c r="S4" t="n">
-        <v>0.13</v>
+        <v>4.0592</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0882</v>
+        <v>0.5678</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0418</v>
+        <v>3.4914</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0895</v>
+        <v>-5.9147</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6342</v>
+        <v>0.4882</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5447</v>
+        <v>-6.403</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5242</v>
+        <v>-2.4719</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8348</v>
+        <v>-1.7823</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6894</v>
+        <v>-0.6894999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7548000000000001</v>
@@ -844,13 +844,13 @@
         <v>0.4552</v>
       </c>
       <c r="S5" t="n">
-        <v>2.211</v>
+        <v>1.2635</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2666</v>
+        <v>1.319</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0556</v>
+        <v>-0.05549999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9317</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.6772</v>
+        <v>-5.0238</v>
       </c>
       <c r="E6" t="n">
-        <v>19.2926</v>
+        <v>-0.1149</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.9698</v>
+        <v>-4.9091</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7515</v>
+        <v>-0.2262999999999995</v>
       </c>
       <c r="H6" t="n">
-        <v>11.3568</v>
+        <v>-15.3874</v>
       </c>
       <c r="I6" t="n">
-        <v>-9.605499999999999</v>
+        <v>15.1611</v>
       </c>
       <c r="J6" t="n">
-        <v>22.4505</v>
+        <v>16.1051</v>
       </c>
       <c r="K6" t="n">
-        <v>17.572</v>
+        <v>0.02209999999999926</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8779</v>
+        <v>16.0828</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.6988</v>
+        <v>-16.3313</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.2153</v>
+        <v>-15.4096</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.4837</v>
+        <v>-0.9219000000000002</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.2434</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-29.5926</v>
+        <v>-27.9989</v>
       </c>
       <c r="R6" t="n">
-        <v>19.349</v>
+        <v>26.1778</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8523</v>
+        <v>-4.2546</v>
       </c>
       <c r="T6" t="n">
-        <v>10.8365</v>
+        <v>-3.56</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.9844</v>
+        <v>-0.6945</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.03760000000000002</v>
+        <v>1.2782</v>
       </c>
       <c r="W6" t="n">
-        <v>15.5979</v>
+        <v>15.3389</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.6352</v>
+        <v>-14.0607</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.887000000000002</v>
+        <v>-6.5661</v>
       </c>
       <c r="E7" t="n">
-        <v>7.6061</v>
+        <v>-3.0467</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.4928</v>
+        <v>-3.5193</v>
       </c>
       <c r="G7" t="n">
-        <v>7.847200000000001</v>
+        <v>-7.3171</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7103</v>
+        <v>-0.3845999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1367</v>
+        <v>-6.9323</v>
       </c>
       <c r="J7" t="n">
-        <v>33.4943</v>
+        <v>-0.5920999999999998</v>
       </c>
       <c r="K7" t="n">
-        <v>24.6687</v>
+        <v>1.2271</v>
       </c>
       <c r="L7" t="n">
-        <v>8.8248</v>
+        <v>-1.8192</v>
       </c>
       <c r="M7" t="n">
-        <v>-25.6473</v>
+        <v>-6.725000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-22.9585</v>
+        <v>-1.6118</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6883</v>
+        <v>-5.113300000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2276000000000005</v>
+        <v>6.1459</v>
       </c>
       <c r="Q7" t="n">
-        <v>-43.0224</v>
+        <v>-1.5935</v>
       </c>
       <c r="R7" t="n">
-        <v>43.25</v>
+        <v>7.7393</v>
       </c>
       <c r="S7" t="n">
-        <v>3.741400000000001</v>
+        <v>-2.2843</v>
       </c>
       <c r="T7" t="n">
-        <v>5.1772</v>
+        <v>-0.08729999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4351</v>
+        <v>-2.1969</v>
       </c>
       <c r="V7" t="n">
-        <v>-17.703</v>
+        <v>-3.1107</v>
       </c>
       <c r="W7" t="n">
-        <v>11.9576</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>-29.6605</v>
+        <v>-2.3368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.5313</v>
+        <v>-6.9002</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4439</v>
+        <v>-8.6371</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.0872</v>
+        <v>1.7371</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.3171</v>
+        <v>-5.0428</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3845999999999999</v>
+        <v>-0.8967999999999998</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.9323</v>
+        <v>-4.1461</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5920999999999998</v>
+        <v>-0.7573000000000002</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2271</v>
+        <v>0.4299000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8192</v>
+        <v>-1.1872</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.725000000000001</v>
+        <v>-4.2856</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6118</v>
+        <v>-1.3267</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.113300000000001</v>
+        <v>-2.9589</v>
       </c>
       <c r="P8" t="n">
-        <v>6.1459</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5935</v>
+        <v>-9.1053</v>
       </c>
       <c r="R8" t="n">
-        <v>7.7393</v>
+        <v>10.4711</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.2494</v>
+        <v>-1.3939</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4844</v>
+        <v>-0.409</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.7646</v>
+        <v>-0.9848999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1107</v>
+        <v>-1.8296</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7739</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3368</v>
+        <v>-3.4638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.465800000000002</v>
+        <v>-7.228800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.093800000000001</v>
+        <v>12.5067</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.3718</v>
+        <v>-19.7354</v>
       </c>
       <c r="G9" t="n">
-        <v>-22.5377</v>
+        <v>1.7515</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.2383</v>
+        <v>11.3568</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.2995</v>
+        <v>-9.605499999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.724399999999999</v>
+        <v>22.4505</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.0867</v>
+        <v>17.572</v>
       </c>
       <c r="L9" t="n">
-        <v>5.811300000000001</v>
+        <v>4.8779</v>
       </c>
       <c r="M9" t="n">
-        <v>-24.2623</v>
+        <v>-20.6988</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.1516</v>
+        <v>-6.2153</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.1104</v>
+        <v>-14.4837</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5526</v>
+        <v>-10.2434</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.983</v>
+        <v>-29.5926</v>
       </c>
       <c r="R9" t="n">
-        <v>22.5357</v>
+        <v>19.349</v>
       </c>
       <c r="S9" t="n">
-        <v>10.0309</v>
+        <v>1.301</v>
       </c>
       <c r="T9" t="n">
-        <v>3.868</v>
+        <v>4.0506</v>
       </c>
       <c r="U9" t="n">
-        <v>6.162599999999999</v>
+        <v>-2.7498</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5116</v>
+        <v>-0.03760000000000002</v>
       </c>
       <c r="W9" t="n">
-        <v>11.2967</v>
+        <v>15.5979</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.8081</v>
+        <v>-15.6352</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.7141</v>
+        <v>-12.0252</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.5707</v>
+        <v>-8.948</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8567000000000007</v>
+        <v>-3.0773</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.0428</v>
+        <v>-7.7455</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8967999999999998</v>
+        <v>-1.7852</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.1461</v>
+        <v>-5.9602</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7573000000000002</v>
+        <v>-4.1204</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4299000000000001</v>
+        <v>0.7443000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1872</v>
+        <v>-4.8648</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.2856</v>
+        <v>-3.6248</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3267</v>
+        <v>-2.5297</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.9589</v>
+        <v>-1.0953</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3658</v>
+        <v>-2.5038</v>
       </c>
       <c r="Q10" t="n">
-        <v>-9.1053</v>
+        <v>-5.6909</v>
       </c>
       <c r="R10" t="n">
-        <v>10.4711</v>
+        <v>3.187</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.2077</v>
+        <v>-1.1477</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.3422</v>
+        <v>-0.2262999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.8653</v>
+        <v>-0.9214</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8296</v>
+        <v>-0.6281000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6342</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4638</v>
+        <v>-1.7176</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.5165</v>
+        <v>-13.5711</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5571</v>
+        <v>-2.382400000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.9596</v>
+        <v>-11.1883</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2262999999999995</v>
+        <v>-22.5377</v>
       </c>
       <c r="H11" t="n">
-        <v>-15.3874</v>
+        <v>-17.2383</v>
       </c>
       <c r="I11" t="n">
-        <v>15.1611</v>
+        <v>-5.2995</v>
       </c>
       <c r="J11" t="n">
-        <v>16.1051</v>
+        <v>1.724399999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02209999999999926</v>
+        <v>-4.0867</v>
       </c>
       <c r="L11" t="n">
-        <v>16.0828</v>
+        <v>5.811300000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-16.3313</v>
+        <v>-24.2623</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.4096</v>
+        <v>-13.1516</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9219000000000002</v>
+        <v>-11.1104</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8211</v>
+        <v>4.5526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-27.9989</v>
+        <v>-17.983</v>
       </c>
       <c r="R11" t="n">
-        <v>26.1778</v>
+        <v>22.5357</v>
       </c>
       <c r="S11" t="n">
-        <v>-11.7477</v>
+        <v>5.9257</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.0024</v>
+        <v>2.5794</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.745</v>
+        <v>3.3462</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2782</v>
+        <v>-1.5116</v>
       </c>
       <c r="W11" t="n">
-        <v>15.3389</v>
+        <v>11.2967</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.0607</v>
+        <v>-12.8081</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.3053</v>
+        <v>-13.5794</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.4253</v>
+        <v>-13.3904</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1201000000000001</v>
+        <v>-0.1890000000000005</v>
       </c>
       <c r="G12" t="n">
         <v>-19.0556</v>
@@ -1390,13 +1390,13 @@
         <v>17.0724</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04690000000000015</v>
+        <v>-0.2275000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.91</v>
+        <v>-0.8750000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9566000000000001</v>
+        <v>0.6475</v>
       </c>
       <c r="V12" t="n">
         <v>5.7033</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.1761</v>
+        <v>-14.4693</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.2508</v>
+        <v>-0.2595999999999989</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9253</v>
+        <v>-14.2101</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.7455</v>
+        <v>7.847200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7852</v>
+        <v>1.7103</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.9602</v>
+        <v>6.1367</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1204</v>
+        <v>33.4943</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7443000000000001</v>
+        <v>24.6687</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.8648</v>
+        <v>8.8248</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6248</v>
+        <v>-25.6473</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.5297</v>
+        <v>-22.9585</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0953</v>
+        <v>-2.6883</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5038</v>
+        <v>0.2276000000000005</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.6909</v>
+        <v>-43.0224</v>
       </c>
       <c r="R13" t="n">
-        <v>3.187</v>
+        <v>43.25</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2985</v>
+        <v>-4.8409</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5291</v>
+        <v>-2.688600000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7694</v>
+        <v>-2.1527</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6281000000000001</v>
+        <v>-17.703</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0895</v>
+        <v>11.9576</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7176</v>
+        <v>-29.6605</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.9295</v>
+        <v>-14.6507</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.0493</v>
+        <v>-12.802</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.88</v>
+        <v>-1.8486</v>
       </c>
       <c r="G14" t="n">
         <v>-9.2277</v>
@@ -1546,13 +1546,13 @@
         <v>4.5526</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.345499999999999</v>
+        <v>-3.0669</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.3043</v>
+        <v>-2.0571</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0412</v>
+        <v>-1.0098</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9009</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.4759</v>
+        <v>-15.755</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6258000000000008</v>
+        <v>-10.62</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.1018</v>
+        <v>-5.1349</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.215199999999999</v>
+        <v>-10.0952</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.2292</v>
+        <v>-5.9337</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.985800000000001</v>
+        <v>-4.1615</v>
       </c>
       <c r="J15" t="n">
-        <v>25.274</v>
+        <v>-5.9968</v>
       </c>
       <c r="K15" t="n">
-        <v>17.3251</v>
+        <v>-2.1975</v>
       </c>
       <c r="L15" t="n">
-        <v>7.948899999999999</v>
+        <v>-3.7992</v>
       </c>
       <c r="M15" t="n">
-        <v>-34.4891</v>
+        <v>-4.0984</v>
       </c>
       <c r="N15" t="n">
-        <v>-20.5544</v>
+        <v>-3.7362</v>
       </c>
       <c r="O15" t="n">
-        <v>-13.9346</v>
+        <v>-0.3623</v>
       </c>
       <c r="P15" t="n">
-        <v>-19.8043</v>
+        <v>-4.325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-56.2251</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>36.4213</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>4.518400000000001</v>
+        <v>-0.2454</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6944</v>
+        <v>-0.02199999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8242999999999998</v>
+        <v>-0.2234</v>
       </c>
       <c r="V15" t="n">
-        <v>8.0245</v>
+        <v>-1.0894</v>
       </c>
       <c r="W15" t="n">
-        <v>27.883</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.8582</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-18.4342</v>
+        <v>-17.0532</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.7033</v>
+        <v>0.2293999999999983</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.7309</v>
+        <v>-17.2826</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.0952</v>
+        <v>-9.215199999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.9337</v>
+        <v>-3.2292</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.1615</v>
+        <v>-5.985800000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.9968</v>
+        <v>25.274</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.1975</v>
+        <v>17.3251</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.7992</v>
+        <v>7.948899999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.0984</v>
+        <v>-34.4891</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.7362</v>
+        <v>-20.5544</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3623</v>
+        <v>-13.9346</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.325</v>
+        <v>-19.8043</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.690799999999999</v>
+        <v>-56.2251</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3658</v>
+        <v>36.4213</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.9246</v>
+        <v>3.9413</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.1052</v>
+        <v>3.2975</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8194</v>
+        <v>0.6436000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0894</v>
+        <v>8.0245</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0895</v>
+        <v>27.883</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1789</v>
+        <v>-19.8582</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-24.4285</v>
+        <v>-19.8165</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.441400000000002</v>
+        <v>-4.218399999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.9874</v>
+        <v>-15.5979</v>
       </c>
       <c r="G17" t="n">
         <v>-18.3541</v>
@@ -1780,13 +1780,13 @@
         <v>27.5436</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.0688</v>
+        <v>-5.457</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.345600000000001</v>
+        <v>-2.1234</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.7229</v>
+        <v>-3.3338</v>
       </c>
       <c r="V17" t="n">
         <v>-3.744800000000001</v>
@@ -1813,13 +1813,13 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-28.7011</v>
+        <v>-24.8562</v>
       </c>
       <c r="E18" t="n">
-        <v>-25.1621</v>
+        <v>-21.2879</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5392</v>
+        <v>-3.5682</v>
       </c>
       <c r="G18" t="n">
         <v>-15.7332</v>
@@ -1858,13 +1858,13 @@
         <v>13.2029</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.0296</v>
+        <v>-3.1847</v>
       </c>
       <c r="T18" t="n">
-        <v>-6.0148</v>
+        <v>-2.1408</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0148</v>
+        <v>-1.0439</v>
       </c>
       <c r="V18" t="n">
         <v>3.394699999999999</v>
@@ -1891,13 +1891,13 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.0301</v>
+        <v>-34.3743</v>
       </c>
       <c r="E19" t="n">
-        <v>-36.4637</v>
+        <v>-34.6657</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5664</v>
+        <v>0.2912000000000003</v>
       </c>
       <c r="G19" t="n">
         <v>-27.3827</v>
@@ -1936,13 +1936,13 @@
         <v>22.3079</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.723100000000001</v>
+        <v>-2.0671</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.6996</v>
+        <v>-0.9013000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.0239</v>
+        <v>-1.166</v>
       </c>
       <c r="V19" t="n">
         <v>5.774100000000001</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>-48.9246</v>
+        <v>-40.5686</v>
       </c>
       <c r="E20" t="n">
-        <v>-29.0718</v>
+        <v>-6.861200000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.8532</v>
+        <v>-33.7077</v>
       </c>
       <c r="G20" t="n">
-        <v>-26.8912</v>
+        <v>4.856700000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-15.502</v>
+        <v>-14.225</v>
       </c>
       <c r="I20" t="n">
-        <v>-11.3891</v>
+        <v>19.0816</v>
       </c>
       <c r="J20" t="n">
-        <v>10.1133</v>
+        <v>41.9074</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4154</v>
+        <v>6.3367</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6982</v>
+        <v>35.5711</v>
       </c>
       <c r="M20" t="n">
-        <v>-37.0044</v>
+        <v>-37.0507</v>
       </c>
       <c r="N20" t="n">
-        <v>-18.9176</v>
+        <v>-20.5617</v>
       </c>
       <c r="O20" t="n">
-        <v>-18.0872</v>
+        <v>-16.4893</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.5118</v>
+        <v>-14.3407</v>
       </c>
       <c r="Q20" t="n">
-        <v>-43.0223</v>
+        <v>-61.0053</v>
       </c>
       <c r="R20" t="n">
-        <v>35.5105</v>
+        <v>46.6647</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.055299999999999</v>
+        <v>-11.4555</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.2772</v>
+        <v>-4.9956</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.778</v>
+        <v>-6.4604</v>
       </c>
       <c r="V20" t="n">
-        <v>-7.4659</v>
+        <v>-19.6286</v>
       </c>
       <c r="W20" t="n">
-        <v>8.1143</v>
+        <v>17.2324</v>
       </c>
       <c r="X20" t="n">
-        <v>-15.5806</v>
+        <v>-36.8611</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-59.4448</v>
+        <v>-44.535</v>
       </c>
       <c r="E21" t="n">
-        <v>-17.2571</v>
+        <v>-25.3505</v>
       </c>
       <c r="F21" t="n">
-        <v>-42.1877</v>
+        <v>-19.1842</v>
       </c>
       <c r="G21" t="n">
-        <v>4.856700000000001</v>
+        <v>-26.8912</v>
       </c>
       <c r="H21" t="n">
-        <v>-14.225</v>
+        <v>-15.502</v>
       </c>
       <c r="I21" t="n">
-        <v>19.0816</v>
+        <v>-11.3891</v>
       </c>
       <c r="J21" t="n">
-        <v>41.9074</v>
+        <v>10.1133</v>
       </c>
       <c r="K21" t="n">
-        <v>6.3367</v>
+        <v>3.4154</v>
       </c>
       <c r="L21" t="n">
-        <v>35.5711</v>
+        <v>6.6982</v>
       </c>
       <c r="M21" t="n">
-        <v>-37.0507</v>
+        <v>-37.0044</v>
       </c>
       <c r="N21" t="n">
-        <v>-20.5617</v>
+        <v>-18.9176</v>
       </c>
       <c r="O21" t="n">
-        <v>-16.4893</v>
+        <v>-18.0872</v>
       </c>
       <c r="P21" t="n">
-        <v>-14.3407</v>
+        <v>-7.5118</v>
       </c>
       <c r="Q21" t="n">
-        <v>-61.0053</v>
+        <v>-43.0223</v>
       </c>
       <c r="R21" t="n">
-        <v>46.6647</v>
+        <v>35.5105</v>
       </c>
       <c r="S21" t="n">
-        <v>-30.3316</v>
+        <v>-2.6659</v>
       </c>
       <c r="T21" t="n">
-        <v>-15.3913</v>
+        <v>-0.5564</v>
       </c>
       <c r="U21" t="n">
-        <v>-14.9399</v>
+        <v>-2.1096</v>
       </c>
       <c r="V21" t="n">
-        <v>-19.6286</v>
+        <v>-7.4659</v>
       </c>
       <c r="W21" t="n">
-        <v>17.2324</v>
+        <v>8.1143</v>
       </c>
       <c r="X21" t="n">
-        <v>-36.8611</v>
+        <v>-15.5806</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-74.5311</v>
+        <v>-57.6134</v>
       </c>
       <c r="E22" t="n">
-        <v>-52.7534</v>
+        <v>-38.6997</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.7779</v>
+        <v>-18.9136</v>
       </c>
       <c r="G22" t="n">
         <v>-21.2315</v>
@@ -2170,13 +2170,13 @@
         <v>46.6648</v>
       </c>
       <c r="S22" t="n">
-        <v>-31.0811</v>
+        <v>-14.1627</v>
       </c>
       <c r="T22" t="n">
-        <v>-23.5153</v>
+        <v>-9.462199999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-7.5655</v>
+        <v>-4.7014</v>
       </c>
       <c r="V22" t="n">
         <v>14.4299</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>-296.997</v>
+        <v>-269.7701</v>
       </c>
       <c r="E23" t="n">
-        <v>-102.847</v>
+        <v>-89.8329</v>
       </c>
       <c r="F23" t="n">
-        <v>-194.1502</v>
+        <v>-179.9363</v>
       </c>
       <c r="G23" t="n">
         <v>-190.6962</v>
@@ -2227,7 +2227,7 @@
         <v>99.61970000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>94.46000000000001</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-384.7763</v>
@@ -2248,16 +2248,16 @@
         <v>462.0938</v>
       </c>
       <c r="S23" t="n">
-        <v>-60.3889</v>
+        <v>-33.16070000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-25.5961</v>
+        <v>-12.5846</v>
       </c>
       <c r="U23" t="n">
-        <v>-34.7907</v>
+        <v>-20.5784</v>
       </c>
       <c r="V23" t="n">
-        <v>65.6277</v>
+        <v>65.62769999999999</v>
       </c>
       <c r="W23" t="n">
         <v>302.3031</v>
